--- a/clan_jagdflugzeug.xlsx
+++ b/clan_jagdflugzeug.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="186">
   <si>
     <t>Клан [LUFT] Jagdflugzeug  -  сортировка по полковым очкам (возрастание)</t>
   </si>
@@ -70,70 +70,253 @@
     <t>15.10.2014</t>
   </si>
   <si>
+    <t>zéus</t>
+  </si>
+  <si>
+    <t>08.10.2021</t>
+  </si>
+  <si>
+    <t>Küchler</t>
+  </si>
+  <si>
+    <t>19.12.2023</t>
+  </si>
+  <si>
+    <t>NoSkill2010</t>
+  </si>
+  <si>
+    <t>20.08.2024</t>
+  </si>
+  <si>
+    <t>aserda</t>
+  </si>
+  <si>
+    <t>14.10.2025</t>
+  </si>
+  <si>
+    <t>NеgaT1vе</t>
+  </si>
+  <si>
+    <t>28.12.2025</t>
+  </si>
+  <si>
+    <t>zeroxsite</t>
+  </si>
+  <si>
+    <t>12.01.2026</t>
+  </si>
+  <si>
+    <t>Northfield</t>
+  </si>
+  <si>
+    <t>13.01.2026</t>
+  </si>
+  <si>
+    <t>cot1ne_tolstey</t>
+  </si>
+  <si>
+    <t>12.02.2026</t>
+  </si>
+  <si>
+    <t>_AGYREZ777_</t>
+  </si>
+  <si>
+    <t>30.03.2026</t>
+  </si>
+  <si>
+    <t>Pivnoy_Okkultist</t>
+  </si>
+  <si>
+    <t>04.04.2026</t>
+  </si>
+  <si>
+    <t>Ричерд</t>
+  </si>
+  <si>
+    <t>Λngel Of Death</t>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+  </si>
+  <si>
+    <t>danii4kin</t>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+  </si>
+  <si>
+    <t>Рак</t>
+  </si>
+  <si>
+    <t>14.04.2026</t>
+  </si>
+  <si>
+    <t>Terminator20387</t>
+  </si>
+  <si>
+    <t>16.04.2026</t>
+  </si>
+  <si>
+    <t>Володя_хороший</t>
+  </si>
+  <si>
+    <t>porkill2013</t>
+  </si>
+  <si>
+    <t>17.04.2026</t>
+  </si>
+  <si>
+    <t>zebsz56h6r</t>
+  </si>
+  <si>
+    <t>22.04.2026</t>
+  </si>
+  <si>
+    <t>мистер_алкаш</t>
+  </si>
+  <si>
+    <t>25.04.2026</t>
+  </si>
+  <si>
+    <t>Vlados_67rus</t>
+  </si>
+  <si>
+    <t>13.05.2026</t>
+  </si>
+  <si>
+    <t>arozzs</t>
+  </si>
+  <si>
+    <t>Spenti#1</t>
+  </si>
+  <si>
+    <t>15.05.2026</t>
+  </si>
+  <si>
+    <t>BR1T</t>
+  </si>
+  <si>
+    <t>modic-74</t>
+  </si>
+  <si>
+    <t>Царь ва Дварца</t>
+  </si>
+  <si>
+    <t>18.05.2026</t>
+  </si>
+  <si>
+    <t>Царь Хохловский</t>
+  </si>
+  <si>
+    <t>KATツ</t>
+  </si>
+  <si>
+    <t>20.05.2026</t>
+  </si>
+  <si>
+    <t>danonab</t>
+  </si>
+  <si>
+    <t>Reflundin</t>
+  </si>
+  <si>
+    <t>21.05.2026</t>
+  </si>
+  <si>
+    <t>PaDuOAKTuBHblu</t>
+  </si>
+  <si>
+    <t>mrkalash1337</t>
+  </si>
+  <si>
+    <t>22.05.2026</t>
+  </si>
+  <si>
+    <t>webaxx</t>
+  </si>
+  <si>
+    <t>06.06.2026</t>
+  </si>
+  <si>
+    <t>Reinhard Krause</t>
+  </si>
+  <si>
+    <t>12.06.2026</t>
+  </si>
+  <si>
+    <t>ZveroboyEvil</t>
+  </si>
+  <si>
+    <t>25.06.2026</t>
+  </si>
+  <si>
+    <t>хискач</t>
+  </si>
+  <si>
+    <t>27.06.2026</t>
+  </si>
+  <si>
+    <t>MamKuH_IIITypM</t>
+  </si>
+  <si>
+    <t>28.06.2026</t>
+  </si>
+  <si>
+    <t>RASXOD_YT</t>
+  </si>
+  <si>
+    <t>31.05.2026</t>
+  </si>
+  <si>
+    <t>ASPIRE81454</t>
+  </si>
+  <si>
+    <t>24.06.2026</t>
+  </si>
+  <si>
     <t>Fridhelm_Winter_</t>
   </si>
   <si>
     <t>07.01.2016</t>
   </si>
   <si>
-    <t>zéus</t>
-  </si>
-  <si>
-    <t>08.10.2021</t>
-  </si>
-  <si>
-    <t>Küchler</t>
-  </si>
-  <si>
-    <t>19.12.2023</t>
-  </si>
-  <si>
-    <t>NoSkill2010</t>
-  </si>
-  <si>
-    <t>20.08.2024</t>
-  </si>
-  <si>
-    <t>aserda</t>
-  </si>
-  <si>
-    <t>14.10.2025</t>
-  </si>
-  <si>
-    <t>NеgaT1vе</t>
-  </si>
-  <si>
-    <t>28.12.2025</t>
-  </si>
-  <si>
-    <t>zeroxsite</t>
-  </si>
-  <si>
-    <t>12.01.2026</t>
-  </si>
-  <si>
-    <t>Northfield</t>
-  </si>
-  <si>
-    <t>13.01.2026</t>
-  </si>
-  <si>
-    <t>cot1ne_tolstey</t>
-  </si>
-  <si>
-    <t>12.02.2026</t>
-  </si>
-  <si>
-    <t>_AGYREZ777_</t>
-  </si>
-  <si>
-    <t>30.03.2026</t>
-  </si>
-  <si>
-    <t>Pivnoy_Okkultist</t>
-  </si>
-  <si>
-    <t>04.04.2026</t>
+    <t>Жубидух</t>
+  </si>
+  <si>
+    <t>16.01.2026</t>
+  </si>
+  <si>
+    <t>viking911a</t>
+  </si>
+  <si>
+    <t>Airton_Senna</t>
+  </si>
+  <si>
+    <t>29.06.2026</t>
+  </si>
+  <si>
+    <t>vadim100_5</t>
+  </si>
+  <si>
+    <t>20.04.2026</t>
+  </si>
+  <si>
+    <t>Luganych</t>
+  </si>
+  <si>
+    <t>22.06.2026</t>
+  </si>
+  <si>
+    <t>Turgrim</t>
+  </si>
+  <si>
+    <t>21.10.2025</t>
+  </si>
+  <si>
+    <t>Tr01</t>
+  </si>
+  <si>
+    <t>31.03.2026</t>
   </si>
   <si>
     <t>Иосиф_Фембой</t>
@@ -142,357 +325,183 @@
     <t>Великий крыс</t>
   </si>
   <si>
-    <t>Ричерд</t>
-  </si>
-  <si>
-    <t>Λngel Of Death</t>
-  </si>
-  <si>
-    <t>09.04.2026</t>
-  </si>
-  <si>
-    <t>danii4kin</t>
-  </si>
-  <si>
-    <t>10.04.2026</t>
-  </si>
-  <si>
-    <t>Рак</t>
-  </si>
-  <si>
-    <t>14.04.2026</t>
-  </si>
-  <si>
-    <t>viking911a</t>
-  </si>
-  <si>
-    <t>16.04.2026</t>
-  </si>
-  <si>
-    <t>Terminator20387</t>
-  </si>
-  <si>
-    <t>Володя_хороший</t>
-  </si>
-  <si>
-    <t>porkill2013</t>
-  </si>
-  <si>
-    <t>17.04.2026</t>
-  </si>
-  <si>
-    <t>zebsz56h6r</t>
-  </si>
-  <si>
-    <t>22.04.2026</t>
-  </si>
-  <si>
-    <t>мистер_алкаш</t>
-  </si>
-  <si>
-    <t>25.04.2026</t>
-  </si>
-  <si>
-    <t>Ruslanka_010</t>
+    <t>wertyfox12</t>
+  </si>
+  <si>
+    <t>22.12.2025</t>
+  </si>
+  <si>
+    <t>_EcTb_TTpo6uTue_</t>
+  </si>
+  <si>
+    <t>_Ruffians_</t>
+  </si>
+  <si>
+    <t>17.02.2024</t>
+  </si>
+  <si>
+    <t>Как Суворов Но лучше</t>
+  </si>
+  <si>
+    <t>11.01.2024</t>
+  </si>
+  <si>
+    <t>Dr_Hermann</t>
+  </si>
+  <si>
+    <t>Hans_Kelner</t>
+  </si>
+  <si>
+    <t>19.11.2025</t>
+  </si>
+  <si>
+    <t>tkachik98</t>
+  </si>
+  <si>
+    <t>25.03.2023</t>
+  </si>
+  <si>
+    <t>Günsche</t>
+  </si>
+  <si>
+    <t>04.06.2022</t>
+  </si>
+  <si>
+    <t>---BeS---</t>
+  </si>
+  <si>
+    <t>TheBlackCreator</t>
+  </si>
+  <si>
+    <t>11.05.2026</t>
+  </si>
+  <si>
+    <t>NikitaPv</t>
+  </si>
+  <si>
+    <t>Nakikliks</t>
+  </si>
+  <si>
+    <t>09.08.2025</t>
+  </si>
+  <si>
+    <t>Max_Gomel</t>
+  </si>
+  <si>
+    <t>25.01.2024</t>
+  </si>
+  <si>
+    <t>rarawi ЁЖИК</t>
+  </si>
+  <si>
+    <t>NIKKI_7</t>
+  </si>
+  <si>
+    <t>Napalm_light</t>
+  </si>
+  <si>
+    <t>Офицер</t>
+  </si>
+  <si>
+    <t>26.05.2016</t>
+  </si>
+  <si>
+    <t>✓ OK</t>
+  </si>
+  <si>
+    <t>Мишаня_Литэноржи</t>
+  </si>
+  <si>
+    <t>LolSkill2010</t>
+  </si>
+  <si>
+    <t>10.01.2024</t>
+  </si>
+  <si>
+    <t>POrChiK</t>
+  </si>
+  <si>
+    <t>Сержант</t>
+  </si>
+  <si>
+    <t>16.09.2024</t>
+  </si>
+  <si>
+    <t>Manfred_Moeller</t>
+  </si>
+  <si>
+    <t>30.07.2013</t>
+  </si>
+  <si>
+    <t>Erich Hartmann-1</t>
+  </si>
+  <si>
+    <t>11.04.2026</t>
+  </si>
+  <si>
+    <t>Afro2ziak</t>
+  </si>
+  <si>
+    <t>11.02.2024</t>
+  </si>
+  <si>
+    <t>scorpion5638</t>
+  </si>
+  <si>
+    <t>Sergeant Hunter</t>
+  </si>
+  <si>
+    <t>29.01.2026</t>
+  </si>
+  <si>
+    <t>RazBanBis</t>
+  </si>
+  <si>
+    <t>07.03.2026</t>
+  </si>
+  <si>
+    <t>Tilarids</t>
+  </si>
+  <si>
+    <t>20.12.2022</t>
+  </si>
+  <si>
+    <t>Kirilka_</t>
+  </si>
+  <si>
+    <t>29.03.2026</t>
+  </si>
+  <si>
+    <t>MaceZzzz</t>
+  </si>
+  <si>
+    <t>10.12.2023</t>
+  </si>
+  <si>
+    <t>Лёха Барон</t>
+  </si>
+  <si>
+    <t>09.06.2026</t>
+  </si>
+  <si>
+    <t>OPK_KILLER</t>
+  </si>
+  <si>
+    <t>09.08.2022</t>
+  </si>
+  <si>
+    <t>Twister267</t>
+  </si>
+  <si>
+    <t>16.03.2024</t>
+  </si>
+  <si>
+    <t>_X_InK_DeMoN_X_</t>
   </si>
   <si>
     <t>30.04.2026</t>
   </si>
   <si>
-    <t>Vlados_67rus</t>
-  </si>
-  <si>
-    <t>13.05.2026</t>
-  </si>
-  <si>
-    <t>arozzs</t>
-  </si>
-  <si>
-    <t>Spenti#1</t>
-  </si>
-  <si>
-    <t>15.05.2026</t>
-  </si>
-  <si>
-    <t>BR1T</t>
-  </si>
-  <si>
-    <t>modic-74</t>
-  </si>
-  <si>
-    <t>Царь ва Дварца</t>
-  </si>
-  <si>
-    <t>18.05.2026</t>
-  </si>
-  <si>
-    <t>Царь Хохловский</t>
-  </si>
-  <si>
-    <t>KATツ</t>
-  </si>
-  <si>
-    <t>20.05.2026</t>
-  </si>
-  <si>
-    <t>danonab</t>
-  </si>
-  <si>
-    <t>Reflundin</t>
-  </si>
-  <si>
-    <t>21.05.2026</t>
-  </si>
-  <si>
-    <t>PaDuOAKTuBHblu</t>
-  </si>
-  <si>
-    <t>mrkalash1337</t>
-  </si>
-  <si>
-    <t>22.05.2026</t>
-  </si>
-  <si>
-    <t>webaxx</t>
-  </si>
-  <si>
-    <t>06.06.2026</t>
-  </si>
-  <si>
-    <t>Reinhard Krause</t>
-  </si>
-  <si>
-    <t>12.06.2026</t>
-  </si>
-  <si>
-    <t>ZveroboyEvil</t>
-  </si>
-  <si>
-    <t>25.06.2026</t>
-  </si>
-  <si>
-    <t>nyxtouge</t>
-  </si>
-  <si>
-    <t>27.06.2026</t>
-  </si>
-  <si>
-    <t>_Ruffians_</t>
-  </si>
-  <si>
-    <t>17.02.2024</t>
-  </si>
-  <si>
-    <t>RASXOD_YT</t>
-  </si>
-  <si>
-    <t>31.05.2026</t>
-  </si>
-  <si>
-    <t>ASPIRE81454</t>
-  </si>
-  <si>
-    <t>24.06.2026</t>
-  </si>
-  <si>
-    <t>Жубидух</t>
-  </si>
-  <si>
-    <t>16.01.2026</t>
-  </si>
-  <si>
-    <t>vadim100_5</t>
-  </si>
-  <si>
-    <t>20.04.2026</t>
-  </si>
-  <si>
-    <t>Luganych</t>
-  </si>
-  <si>
-    <t>22.06.2026</t>
-  </si>
-  <si>
-    <t>Turgrim</t>
-  </si>
-  <si>
-    <t>21.10.2025</t>
-  </si>
-  <si>
-    <t>Tr01</t>
-  </si>
-  <si>
-    <t>31.03.2026</t>
-  </si>
-  <si>
-    <t>wertyfox12</t>
-  </si>
-  <si>
-    <t>22.12.2025</t>
-  </si>
-  <si>
-    <t>tkachik98</t>
-  </si>
-  <si>
-    <t>25.03.2023</t>
-  </si>
-  <si>
-    <t>_EcTb_TTpo6uTue_</t>
-  </si>
-  <si>
-    <t>Dr_Hermann</t>
-  </si>
-  <si>
-    <t>Как Суворов Но лучше</t>
-  </si>
-  <si>
-    <t>11.01.2024</t>
-  </si>
-  <si>
-    <t>Hans_Kelner</t>
-  </si>
-  <si>
-    <t>19.11.2025</t>
-  </si>
-  <si>
-    <t>TheBlackCreator</t>
-  </si>
-  <si>
-    <t>11.05.2026</t>
-  </si>
-  <si>
-    <t>NikitaPv</t>
-  </si>
-  <si>
-    <t>Günsche</t>
-  </si>
-  <si>
-    <t>04.06.2022</t>
-  </si>
-  <si>
-    <t>---BeS---</t>
-  </si>
-  <si>
-    <t>Nakikliks</t>
-  </si>
-  <si>
-    <t>09.08.2025</t>
-  </si>
-  <si>
-    <t>Napalm_light</t>
-  </si>
-  <si>
-    <t>Офицер</t>
-  </si>
-  <si>
-    <t>26.05.2016</t>
-  </si>
-  <si>
-    <t>NIKKI_7</t>
-  </si>
-  <si>
-    <t>Max_Gomel</t>
-  </si>
-  <si>
-    <t>25.01.2024</t>
-  </si>
-  <si>
-    <t>rarawi ЁЖИК</t>
-  </si>
-  <si>
-    <t>POrChiK</t>
-  </si>
-  <si>
-    <t>Сержант</t>
-  </si>
-  <si>
-    <t>16.09.2024</t>
-  </si>
-  <si>
-    <t>Мишаня_Литэноржи</t>
-  </si>
-  <si>
-    <t>Manfred_Moeller</t>
-  </si>
-  <si>
-    <t>30.07.2013</t>
-  </si>
-  <si>
-    <t>LolSkill2010</t>
-  </si>
-  <si>
-    <t>10.01.2024</t>
-  </si>
-  <si>
-    <t>Erich Hartmann-1</t>
-  </si>
-  <si>
-    <t>11.04.2026</t>
-  </si>
-  <si>
-    <t>✓ OK</t>
-  </si>
-  <si>
-    <t>RazBanBis</t>
-  </si>
-  <si>
-    <t>07.03.2026</t>
-  </si>
-  <si>
-    <t>Afro2ziak</t>
-  </si>
-  <si>
-    <t>11.02.2024</t>
-  </si>
-  <si>
-    <t>Лёха Барон</t>
-  </si>
-  <si>
-    <t>09.06.2026</t>
-  </si>
-  <si>
-    <t>Tilarids</t>
-  </si>
-  <si>
-    <t>20.12.2022</t>
-  </si>
-  <si>
-    <t>Sergeant Hunter</t>
-  </si>
-  <si>
-    <t>29.01.2026</t>
-  </si>
-  <si>
-    <t>Kirilka_</t>
-  </si>
-  <si>
-    <t>29.03.2026</t>
-  </si>
-  <si>
-    <t>MaceZzzz</t>
-  </si>
-  <si>
-    <t>10.12.2023</t>
-  </si>
-  <si>
-    <t>scorpion5638</t>
-  </si>
-  <si>
-    <t>OPK_KILLER</t>
-  </si>
-  <si>
-    <t>09.08.2022</t>
-  </si>
-  <si>
-    <t>Twister267</t>
-  </si>
-  <si>
-    <t>16.03.2024</t>
-  </si>
-  <si>
-    <t>_X_InK_DeMoN_X_</t>
-  </si>
-  <si>
     <t>Tkachik_Sr</t>
   </si>
   <si>
@@ -547,22 +556,22 @@
     <t>Всего игроков:</t>
   </si>
   <si>
-    <t>Проблемных (&lt; 1200 очков):</t>
+    <t>Проблемных (&lt; 1000 очков):</t>
   </si>
   <si>
     <t>Новеньких (не учитываются):</t>
   </si>
   <si>
-    <t xml:space="preserve">  🔴 Красный - мало очков, вступил ДО 28.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  🟠 Оранжевый - мало очков, но вступил ПОСЛЕ 28.06.2026 (новенький)</t>
-  </si>
-  <si>
-    <t>Мало очков И вступили ДО 28.06.2026  (порог: 1200)</t>
-  </si>
-  <si>
-    <t>Низкий рейтинг, но вступили ПОСЛЕ 28.06.2026  (порог: 1200)</t>
+    <t xml:space="preserve">  🔴 Красный - мало очков, вступил ДО 01.07.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  🟠 Оранжевый - мало очков, но вступил ПОСЛЕ 01.07.2026 (новенький)</t>
+  </si>
+  <si>
+    <t>Мало очков И вступили ДО 01.07.2026  (порог: 1000)</t>
+  </si>
+  <si>
+    <t>Низкий рейтинг, но вступили ПОСЛЕ 01.07.2026  (порог: 1000)</t>
   </si>
 </sst>
 </file>
@@ -873,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="5.859375" customWidth="true"/>
@@ -1203,7 +1212,7 @@
         <v>0.0</v>
       </c>
       <c r="E17" t="s" s="3">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F17" t="s" s="3">
         <v>10</v>
@@ -1214,16 +1223,16 @@
         <v>16.0</v>
       </c>
       <c r="B18" t="s" s="3">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D18" t="n" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="s" s="3">
         <v>40</v>
-      </c>
-      <c r="C18" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D18" t="n" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="E18" t="s" s="3">
-        <v>39</v>
       </c>
       <c r="F18" t="s" s="3">
         <v>10</v>
@@ -1243,7 +1252,7 @@
         <v>0.0</v>
       </c>
       <c r="E19" t="s" s="3">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s" s="3">
         <v>10</v>
@@ -1254,7 +1263,7 @@
         <v>18.0</v>
       </c>
       <c r="B20" t="s" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s" s="3">
         <v>14</v>
@@ -1263,7 +1272,7 @@
         <v>0.0</v>
       </c>
       <c r="E20" t="s" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s" s="3">
         <v>10</v>
@@ -1274,7 +1283,7 @@
         <v>19.0</v>
       </c>
       <c r="B21" t="s" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s" s="3">
         <v>14</v>
@@ -1283,7 +1292,7 @@
         <v>0.0</v>
       </c>
       <c r="E21" t="s" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F21" t="s" s="3">
         <v>10</v>
@@ -1294,7 +1303,7 @@
         <v>20.0</v>
       </c>
       <c r="B22" t="s" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s" s="3">
         <v>14</v>
@@ -1314,7 +1323,7 @@
         <v>21.0</v>
       </c>
       <c r="B23" t="s" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s" s="3">
         <v>14</v>
@@ -1323,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="E23" t="s" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F23" t="s" s="3">
         <v>10</v>
@@ -1334,7 +1343,7 @@
         <v>22.0</v>
       </c>
       <c r="B24" t="s" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s" s="3">
         <v>14</v>
@@ -1343,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="E24" t="s" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s" s="3">
         <v>10</v>
@@ -1354,7 +1363,7 @@
         <v>23.0</v>
       </c>
       <c r="B25" t="s" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s" s="3">
         <v>14</v>
@@ -1363,7 +1372,7 @@
         <v>0.0</v>
       </c>
       <c r="E25" t="s" s="3">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F25" t="s" s="3">
         <v>10</v>
@@ -1374,7 +1383,7 @@
         <v>24.0</v>
       </c>
       <c r="B26" t="s" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s" s="3">
         <v>14</v>
@@ -1383,7 +1392,7 @@
         <v>0.0</v>
       </c>
       <c r="E26" t="s" s="3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F26" t="s" s="3">
         <v>10</v>
@@ -1394,7 +1403,7 @@
         <v>25.0</v>
       </c>
       <c r="B27" t="s" s="3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s" s="3">
         <v>14</v>
@@ -1403,7 +1412,7 @@
         <v>0.0</v>
       </c>
       <c r="E27" t="s" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F27" t="s" s="3">
         <v>10</v>
@@ -1414,7 +1423,7 @@
         <v>26.0</v>
       </c>
       <c r="B28" t="s" s="3">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s" s="3">
         <v>14</v>
@@ -1423,7 +1432,7 @@
         <v>0.0</v>
       </c>
       <c r="E28" t="s" s="3">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s" s="3">
         <v>10</v>
@@ -1434,7 +1443,7 @@
         <v>27.0</v>
       </c>
       <c r="B29" t="s" s="3">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s" s="3">
         <v>14</v>
@@ -1454,7 +1463,7 @@
         <v>28.0</v>
       </c>
       <c r="B30" t="s" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s" s="3">
         <v>14</v>
@@ -1463,7 +1472,7 @@
         <v>0.0</v>
       </c>
       <c r="E30" t="s" s="3">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F30" t="s" s="3">
         <v>10</v>
@@ -1563,7 +1572,7 @@
         <v>0.0</v>
       </c>
       <c r="E35" t="s" s="3">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F35" t="s" s="3">
         <v>10</v>
@@ -1574,16 +1583,16 @@
         <v>34.0</v>
       </c>
       <c r="B36" t="s" s="3">
+        <v>69</v>
+      </c>
+      <c r="C36" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D36" t="n" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E36" t="s" s="3">
         <v>68</v>
-      </c>
-      <c r="C36" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D36" t="n" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="E36" t="s" s="3">
-        <v>69</v>
       </c>
       <c r="F36" t="s" s="3">
         <v>10</v>
@@ -1603,7 +1612,7 @@
         <v>0.0</v>
       </c>
       <c r="E37" t="s" s="3">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F37" t="s" s="3">
         <v>10</v>
@@ -1614,7 +1623,7 @@
         <v>36.0</v>
       </c>
       <c r="B38" t="s" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" t="s" s="3">
         <v>14</v>
@@ -1623,7 +1632,7 @@
         <v>0.0</v>
       </c>
       <c r="E38" t="s" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F38" t="s" s="3">
         <v>10</v>
@@ -1634,7 +1643,7 @@
         <v>37.0</v>
       </c>
       <c r="B39" t="s" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C39" t="s" s="3">
         <v>14</v>
@@ -1643,7 +1652,7 @@
         <v>0.0</v>
       </c>
       <c r="E39" t="s" s="3">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F39" t="s" s="3">
         <v>10</v>
@@ -1654,7 +1663,7 @@
         <v>38.0</v>
       </c>
       <c r="B40" t="s" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C40" t="s" s="3">
         <v>14</v>
@@ -1663,7 +1672,7 @@
         <v>0.0</v>
       </c>
       <c r="E40" t="s" s="3">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F40" t="s" s="3">
         <v>10</v>
@@ -1674,7 +1683,7 @@
         <v>39.0</v>
       </c>
       <c r="B41" t="s" s="3">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C41" t="s" s="3">
         <v>14</v>
@@ -1683,7 +1692,7 @@
         <v>0.0</v>
       </c>
       <c r="E41" t="s" s="3">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F41" t="s" s="3">
         <v>10</v>
@@ -1694,7 +1703,7 @@
         <v>40.0</v>
       </c>
       <c r="B42" t="s" s="3">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s" s="3">
         <v>14</v>
@@ -1703,7 +1712,7 @@
         <v>0.0</v>
       </c>
       <c r="E42" t="s" s="3">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F42" t="s" s="3">
         <v>10</v>
@@ -1714,16 +1723,16 @@
         <v>41.0</v>
       </c>
       <c r="B43" t="s" s="3">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C43" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D43" t="n" s="4">
-        <v>0.0</v>
+        <v>61.0</v>
       </c>
       <c r="E43" t="s" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F43" t="s" s="3">
         <v>10</v>
@@ -1734,16 +1743,16 @@
         <v>42.0</v>
       </c>
       <c r="B44" t="s" s="3">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D44" t="n" s="4">
-        <v>0.0</v>
+        <v>61.0</v>
       </c>
       <c r="E44" t="s" s="3">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F44" t="s" s="3">
         <v>10</v>
@@ -1754,16 +1763,16 @@
         <v>43.0</v>
       </c>
       <c r="B45" t="s" s="3">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D45" t="n" s="4">
-        <v>0.0</v>
+        <v>124.0</v>
       </c>
       <c r="E45" t="s" s="3">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F45" t="s" s="3">
         <v>10</v>
@@ -1774,16 +1783,16 @@
         <v>44.0</v>
       </c>
       <c r="B46" t="s" s="3">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D46" t="n" s="4">
-        <v>0.0</v>
+        <v>126.0</v>
       </c>
       <c r="E46" t="s" s="3">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F46" t="s" s="3">
         <v>10</v>
@@ -1794,16 +1803,16 @@
         <v>45.0</v>
       </c>
       <c r="B47" t="s" s="3">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C47" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D47" t="n" s="4">
-        <v>60.0</v>
+        <v>126.0</v>
       </c>
       <c r="E47" t="s" s="3">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F47" t="s" s="3">
         <v>10</v>
@@ -1814,16 +1823,16 @@
         <v>46.0</v>
       </c>
       <c r="B48" t="s" s="3">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C48" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D48" t="n" s="4">
-        <v>61.0</v>
+        <v>148.0</v>
       </c>
       <c r="E48" t="s" s="3">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F48" t="s" s="3">
         <v>10</v>
@@ -1834,16 +1843,16 @@
         <v>47.0</v>
       </c>
       <c r="B49" t="s" s="3">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D49" t="n" s="4">
-        <v>61.0</v>
+        <v>154.0</v>
       </c>
       <c r="E49" t="s" s="3">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F49" t="s" s="3">
         <v>10</v>
@@ -1854,16 +1863,16 @@
         <v>48.0</v>
       </c>
       <c r="B50" t="s" s="3">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C50" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D50" t="n" s="4">
-        <v>126.0</v>
+        <v>159.0</v>
       </c>
       <c r="E50" t="s" s="3">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F50" t="s" s="3">
         <v>10</v>
@@ -1874,16 +1883,16 @@
         <v>49.0</v>
       </c>
       <c r="B51" t="s" s="3">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C51" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D51" t="n" s="4">
-        <v>154.0</v>
+        <v>184.0</v>
       </c>
       <c r="E51" t="s" s="3">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F51" t="s" s="3">
         <v>10</v>
@@ -1894,16 +1903,16 @@
         <v>50.0</v>
       </c>
       <c r="B52" t="s" s="3">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D52" t="n" s="4">
-        <v>159.0</v>
+        <v>215.0</v>
       </c>
       <c r="E52" t="s" s="3">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F52" t="s" s="3">
         <v>10</v>
@@ -1914,16 +1923,16 @@
         <v>51.0</v>
       </c>
       <c r="B53" t="s" s="3">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D53" t="n" s="4">
-        <v>184.0</v>
+        <v>215.0</v>
       </c>
       <c r="E53" t="s" s="3">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="F53" t="s" s="3">
         <v>10</v>
@@ -1934,7 +1943,7 @@
         <v>52.0</v>
       </c>
       <c r="B54" t="s" s="3">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C54" t="s" s="3">
         <v>14</v>
@@ -1943,7 +1952,7 @@
         <v>215.0</v>
       </c>
       <c r="E54" t="s" s="3">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="F54" t="s" s="3">
         <v>10</v>
@@ -1980,10 +1989,10 @@
         <v>14</v>
       </c>
       <c r="D56" t="n" s="4">
-        <v>219.0</v>
+        <v>236.0</v>
       </c>
       <c r="E56" t="s" s="3">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="F56" t="s" s="3">
         <v>10</v>
@@ -1994,16 +2003,16 @@
         <v>55.0</v>
       </c>
       <c r="B57" t="s" s="3">
+        <v>106</v>
+      </c>
+      <c r="C57" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D57" t="n" s="4">
+        <v>272.0</v>
+      </c>
+      <c r="E57" t="s" s="3">
         <v>107</v>
-      </c>
-      <c r="C57" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D57" t="n" s="4">
-        <v>236.0</v>
-      </c>
-      <c r="E57" t="s" s="3">
-        <v>54</v>
       </c>
       <c r="F57" t="s" s="3">
         <v>10</v>
@@ -2020,10 +2029,10 @@
         <v>14</v>
       </c>
       <c r="D58" t="n" s="4">
-        <v>278.0</v>
+        <v>282.0</v>
       </c>
       <c r="E58" t="s" s="3">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="F58" t="s" s="3">
         <v>10</v>
@@ -2034,16 +2043,16 @@
         <v>57.0</v>
       </c>
       <c r="B59" t="s" s="3">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C59" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D59" t="n" s="4">
-        <v>282.0</v>
+        <v>338.0</v>
       </c>
       <c r="E59" t="s" s="3">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="F59" t="s" s="3">
         <v>10</v>
@@ -2080,7 +2089,7 @@
         <v>14</v>
       </c>
       <c r="D61" t="n" s="4">
-        <v>375.0</v>
+        <v>431.0</v>
       </c>
       <c r="E61" t="s" s="3">
         <v>114</v>
@@ -2100,10 +2109,10 @@
         <v>14</v>
       </c>
       <c r="D62" t="n" s="4">
-        <v>401.0</v>
+        <v>468.0</v>
       </c>
       <c r="E62" t="s" s="3">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F62" t="s" s="3">
         <v>10</v>
@@ -2114,16 +2123,16 @@
         <v>61.0</v>
       </c>
       <c r="B63" t="s" s="3">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C63" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D63" t="n" s="4">
-        <v>468.0</v>
+        <v>502.0</v>
       </c>
       <c r="E63" t="s" s="3">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="F63" t="s" s="3">
         <v>10</v>
@@ -2140,10 +2149,10 @@
         <v>14</v>
       </c>
       <c r="D64" t="n" s="4">
-        <v>502.0</v>
+        <v>529.0</v>
       </c>
       <c r="E64" t="s" s="3">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="F64" t="s" s="3">
         <v>10</v>
@@ -2154,16 +2163,16 @@
         <v>63.0</v>
       </c>
       <c r="B65" t="s" s="3">
+        <v>120</v>
+      </c>
+      <c r="C65" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D65" t="n" s="4">
+        <v>555.0</v>
+      </c>
+      <c r="E65" t="s" s="3">
         <v>119</v>
-      </c>
-      <c r="C65" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D65" t="n" s="4">
-        <v>589.0</v>
-      </c>
-      <c r="E65" t="s" s="3">
-        <v>120</v>
       </c>
       <c r="F65" t="s" s="3">
         <v>10</v>
@@ -2177,13 +2186,13 @@
         <v>121</v>
       </c>
       <c r="C66" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D66" t="n" s="4">
+        <v>589.0</v>
+      </c>
+      <c r="E66" t="s" s="3">
         <v>122</v>
-      </c>
-      <c r="D66" t="n" s="4">
-        <v>726.0</v>
-      </c>
-      <c r="E66" t="s" s="3">
-        <v>123</v>
       </c>
       <c r="F66" t="s" s="3">
         <v>10</v>
@@ -2194,16 +2203,16 @@
         <v>65.0</v>
       </c>
       <c r="B67" t="s" s="3">
+        <v>123</v>
+      </c>
+      <c r="C67" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D67" t="n" s="4">
+        <v>808.0</v>
+      </c>
+      <c r="E67" t="s" s="3">
         <v>124</v>
-      </c>
-      <c r="C67" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D67" t="n" s="4">
-        <v>777.0</v>
-      </c>
-      <c r="E67" t="s" s="3">
-        <v>82</v>
       </c>
       <c r="F67" t="s" s="3">
         <v>10</v>
@@ -2220,10 +2229,10 @@
         <v>14</v>
       </c>
       <c r="D68" t="n" s="4">
-        <v>808.0</v>
+        <v>865.0</v>
       </c>
       <c r="E68" t="s" s="3">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="F68" t="s" s="3">
         <v>10</v>
@@ -2234,99 +2243,99 @@
         <v>67.0</v>
       </c>
       <c r="B69" t="s" s="3">
+        <v>126</v>
+      </c>
+      <c r="C69" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D69" t="n" s="4">
+        <v>899.0</v>
+      </c>
+      <c r="E69" t="s" s="3">
+        <v>75</v>
+      </c>
+      <c r="F69" t="s" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" ht="18.0" customHeight="true">
+      <c r="A70" t="n" s="10">
+        <v>68.0</v>
+      </c>
+      <c r="B70" t="s" s="9">
         <v>127</v>
       </c>
-      <c r="C69" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D69" t="n" s="4">
-        <v>835.0</v>
-      </c>
-      <c r="E69" t="s" s="3">
-        <v>82</v>
-      </c>
-      <c r="F69" t="s" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" ht="18.0" customHeight="true">
-      <c r="A70" t="n" s="4">
-        <v>68.0</v>
-      </c>
-      <c r="B70" t="s" s="3">
+      <c r="C70" t="s" s="9">
         <v>128</v>
       </c>
-      <c r="C70" t="s" s="3">
+      <c r="D70" t="n" s="10">
+        <v>1024.0</v>
+      </c>
+      <c r="E70" t="s" s="9">
         <v>129</v>
       </c>
-      <c r="D70" t="n" s="4">
-        <v>957.0</v>
-      </c>
-      <c r="E70" t="s" s="3">
+      <c r="F70" t="s" s="9">
         <v>130</v>
       </c>
-      <c r="F70" t="s" s="3">
-        <v>10</v>
-      </c>
     </row>
     <row r="71" ht="18.0" customHeight="true">
-      <c r="A71" t="n" s="4">
+      <c r="A71" t="n" s="8">
         <v>69.0</v>
       </c>
-      <c r="B71" t="s" s="3">
+      <c r="B71" t="s" s="7">
         <v>131</v>
       </c>
-      <c r="C71" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D71" t="n" s="4">
+      <c r="C71" t="s" s="7">
+        <v>14</v>
+      </c>
+      <c r="D71" t="n" s="8">
         <v>1061.0</v>
       </c>
-      <c r="E71" t="s" s="3">
-        <v>50</v>
-      </c>
-      <c r="F71" t="s" s="3">
-        <v>10</v>
+      <c r="E71" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="F71" t="s" s="7">
+        <v>130</v>
       </c>
     </row>
     <row r="72" ht="18.0" customHeight="true">
-      <c r="A72" t="n" s="4">
+      <c r="A72" t="n" s="10">
         <v>70.0</v>
       </c>
-      <c r="B72" t="s" s="3">
+      <c r="B72" t="s" s="9">
         <v>132</v>
       </c>
-      <c r="C72" t="s" s="3">
-        <v>8</v>
-      </c>
-      <c r="D72" t="n" s="4">
-        <v>1133.0</v>
-      </c>
-      <c r="E72" t="s" s="3">
+      <c r="C72" t="s" s="9">
+        <v>128</v>
+      </c>
+      <c r="D72" t="n" s="10">
+        <v>1190.0</v>
+      </c>
+      <c r="E72" t="s" s="9">
         <v>133</v>
       </c>
-      <c r="F72" t="s" s="3">
-        <v>10</v>
+      <c r="F72" t="s" s="9">
+        <v>130</v>
       </c>
     </row>
     <row r="73" ht="18.0" customHeight="true">
-      <c r="A73" t="n" s="4">
+      <c r="A73" t="n" s="8">
         <v>71.0</v>
       </c>
-      <c r="B73" t="s" s="3">
+      <c r="B73" t="s" s="7">
         <v>134</v>
       </c>
-      <c r="C73" t="s" s="3">
-        <v>122</v>
-      </c>
-      <c r="D73" t="n" s="4">
-        <v>1148.0</v>
-      </c>
-      <c r="E73" t="s" s="3">
+      <c r="C73" t="s" s="7">
         <v>135</v>
       </c>
-      <c r="F73" t="s" s="3">
-        <v>10</v>
+      <c r="D73" t="n" s="8">
+        <v>1199.0</v>
+      </c>
+      <c r="E73" t="s" s="7">
+        <v>136</v>
+      </c>
+      <c r="F73" t="s" s="7">
+        <v>130</v>
       </c>
     </row>
     <row r="74" ht="18.0" customHeight="true">
@@ -2334,19 +2343,19 @@
         <v>72.0</v>
       </c>
       <c r="B74" t="s" s="9">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C74" t="s" s="9">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D74" t="n" s="10">
-        <v>1277.0</v>
+        <v>1237.0</v>
       </c>
       <c r="E74" t="s" s="9">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F74" t="s" s="9">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="75" ht="18.0" customHeight="true">
@@ -2360,13 +2369,13 @@
         <v>14</v>
       </c>
       <c r="D75" t="n" s="8">
-        <v>1320.0</v>
+        <v>1277.0</v>
       </c>
       <c r="E75" t="s" s="7">
         <v>140</v>
       </c>
       <c r="F75" t="s" s="7">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76" ht="18.0" customHeight="true">
@@ -2380,13 +2389,13 @@
         <v>14</v>
       </c>
       <c r="D76" t="n" s="10">
-        <v>1406.0</v>
+        <v>1405.0</v>
       </c>
       <c r="E76" t="s" s="9">
         <v>142</v>
       </c>
       <c r="F76" t="s" s="9">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="77" ht="18.0" customHeight="true">
@@ -2400,13 +2409,13 @@
         <v>14</v>
       </c>
       <c r="D77" t="n" s="8">
-        <v>1414.0</v>
+        <v>1451.0</v>
       </c>
       <c r="E77" t="s" s="7">
-        <v>144</v>
+        <v>68</v>
       </c>
       <c r="F77" t="s" s="7">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="78" ht="18.0" customHeight="true">
@@ -2414,19 +2423,19 @@
         <v>76.0</v>
       </c>
       <c r="B78" t="s" s="9">
+        <v>144</v>
+      </c>
+      <c r="C78" t="s" s="9">
+        <v>14</v>
+      </c>
+      <c r="D78" t="n" s="10">
+        <v>1457.0</v>
+      </c>
+      <c r="E78" t="s" s="9">
         <v>145</v>
       </c>
-      <c r="C78" t="s" s="9">
-        <v>14</v>
-      </c>
-      <c r="D78" t="n" s="10">
-        <v>1419.0</v>
-      </c>
-      <c r="E78" t="s" s="9">
-        <v>146</v>
-      </c>
       <c r="F78" t="s" s="9">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="79" ht="18.0" customHeight="true">
@@ -2434,19 +2443,19 @@
         <v>77.0</v>
       </c>
       <c r="B79" t="s" s="7">
+        <v>146</v>
+      </c>
+      <c r="C79" t="s" s="7">
+        <v>14</v>
+      </c>
+      <c r="D79" t="n" s="8">
+        <v>1462.0</v>
+      </c>
+      <c r="E79" t="s" s="7">
         <v>147</v>
       </c>
-      <c r="C79" t="s" s="7">
-        <v>14</v>
-      </c>
-      <c r="D79" t="n" s="8">
-        <v>1456.0</v>
-      </c>
-      <c r="E79" t="s" s="7">
-        <v>148</v>
-      </c>
       <c r="F79" t="s" s="7">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="80" ht="18.0" customHeight="true">
@@ -2454,19 +2463,19 @@
         <v>78.0</v>
       </c>
       <c r="B80" t="s" s="9">
+        <v>148</v>
+      </c>
+      <c r="C80" t="s" s="9">
+        <v>14</v>
+      </c>
+      <c r="D80" t="n" s="10">
+        <v>1463.0</v>
+      </c>
+      <c r="E80" t="s" s="9">
         <v>149</v>
       </c>
-      <c r="C80" t="s" s="9">
-        <v>14</v>
-      </c>
-      <c r="D80" t="n" s="10">
-        <v>1464.0</v>
-      </c>
-      <c r="E80" t="s" s="9">
-        <v>150</v>
-      </c>
       <c r="F80" t="s" s="9">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="81" ht="18.0" customHeight="true">
@@ -2474,19 +2483,19 @@
         <v>79.0</v>
       </c>
       <c r="B81" t="s" s="7">
+        <v>150</v>
+      </c>
+      <c r="C81" t="s" s="7">
+        <v>14</v>
+      </c>
+      <c r="D81" t="n" s="8">
+        <v>1464.0</v>
+      </c>
+      <c r="E81" t="s" s="7">
         <v>151</v>
       </c>
-      <c r="C81" t="s" s="7">
-        <v>14</v>
-      </c>
-      <c r="D81" t="n" s="8">
-        <v>1471.0</v>
-      </c>
-      <c r="E81" t="s" s="7">
-        <v>152</v>
-      </c>
       <c r="F81" t="s" s="7">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="82" ht="18.0" customHeight="true">
@@ -2494,19 +2503,19 @@
         <v>80.0</v>
       </c>
       <c r="B82" t="s" s="9">
+        <v>152</v>
+      </c>
+      <c r="C82" t="s" s="9">
+        <v>14</v>
+      </c>
+      <c r="D82" t="n" s="10">
+        <v>1466.0</v>
+      </c>
+      <c r="E82" t="s" s="9">
         <v>153</v>
       </c>
-      <c r="C82" t="s" s="9">
-        <v>14</v>
-      </c>
-      <c r="D82" t="n" s="10">
-        <v>1489.0</v>
-      </c>
-      <c r="E82" t="s" s="9">
-        <v>75</v>
-      </c>
       <c r="F82" t="s" s="9">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="83" ht="18.0" customHeight="true">
@@ -2517,16 +2526,16 @@
         <v>154</v>
       </c>
       <c r="C83" t="s" s="7">
-        <v>122</v>
+        <v>14</v>
       </c>
       <c r="D83" t="n" s="8">
-        <v>1500.0</v>
+        <v>1467.0</v>
       </c>
       <c r="E83" t="s" s="7">
         <v>155</v>
       </c>
       <c r="F83" t="s" s="7">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="84" ht="18.0" customHeight="true">
@@ -2537,7 +2546,7 @@
         <v>156</v>
       </c>
       <c r="C84" t="s" s="9">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D84" t="n" s="10">
         <v>1500.0</v>
@@ -2546,7 +2555,7 @@
         <v>157</v>
       </c>
       <c r="F84" t="s" s="9">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="85" ht="18.0" customHeight="true">
@@ -2557,16 +2566,16 @@
         <v>158</v>
       </c>
       <c r="C85" t="s" s="7">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="D85" t="n" s="8">
-        <v>1513.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E85" t="s" s="7">
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="F85" t="s" s="7">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="86" ht="18.0" customHeight="true">
@@ -2574,19 +2583,19 @@
         <v>84.0</v>
       </c>
       <c r="B86" t="s" s="9">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C86" t="s" s="9">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D86" t="n" s="10">
-        <v>1518.0</v>
+        <v>1513.0</v>
       </c>
       <c r="E86" t="s" s="9">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F86" t="s" s="9">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="87" ht="18.0" customHeight="true">
@@ -2594,19 +2603,19 @@
         <v>85.0</v>
       </c>
       <c r="B87" t="s" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C87" t="s" s="7">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D87" t="n" s="8">
-        <v>1538.0</v>
+        <v>1518.0</v>
       </c>
       <c r="E87" t="s" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F87" t="s" s="7">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="88" ht="18.0" customHeight="true">
@@ -2614,19 +2623,19 @@
         <v>86.0</v>
       </c>
       <c r="B88" t="s" s="9">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C88" t="s" s="9">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="D88" t="n" s="10">
-        <v>1546.0</v>
+        <v>1538.0</v>
       </c>
       <c r="E88" t="s" s="9">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="F88" t="s" s="9">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="89" ht="18.0" customHeight="true">
@@ -2634,7 +2643,7 @@
         <v>87.0</v>
       </c>
       <c r="B89" t="s" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C89" t="s" s="7">
         <v>14</v>
@@ -2643,10 +2652,10 @@
         <v>1546.0</v>
       </c>
       <c r="E89" t="s" s="7">
-        <v>39</v>
+        <v>151</v>
       </c>
       <c r="F89" t="s" s="7">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="90" ht="18.0" customHeight="true">
@@ -2654,19 +2663,19 @@
         <v>88.0</v>
       </c>
       <c r="B90" t="s" s="9">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C90" t="s" s="9">
         <v>14</v>
       </c>
       <c r="D90" t="n" s="10">
-        <v>1550.0</v>
+        <v>1546.0</v>
       </c>
       <c r="E90" t="s" s="9">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="F90" t="s" s="9">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="91" ht="18.0" customHeight="true">
@@ -2674,19 +2683,19 @@
         <v>89.0</v>
       </c>
       <c r="B91" t="s" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C91" t="s" s="7">
-        <v>122</v>
+        <v>14</v>
       </c>
       <c r="D91" t="n" s="8">
-        <v>1575.0</v>
+        <v>1550.0</v>
       </c>
       <c r="E91" t="s" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F91" t="s" s="7">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="92" ht="18.0" customHeight="true">
@@ -2694,19 +2703,19 @@
         <v>90.0</v>
       </c>
       <c r="B92" t="s" s="9">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C92" t="s" s="9">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D92" t="n" s="10">
-        <v>1584.0</v>
+        <v>1574.0</v>
       </c>
       <c r="E92" t="s" s="9">
-        <v>54</v>
+        <v>171</v>
       </c>
       <c r="F92" t="s" s="9">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="93" ht="18.0" customHeight="true">
@@ -2714,19 +2723,19 @@
         <v>91.0</v>
       </c>
       <c r="B93" t="s" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C93" t="s" s="7">
-        <v>122</v>
+        <v>14</v>
       </c>
       <c r="D93" t="n" s="8">
-        <v>1594.0</v>
+        <v>1584.0</v>
       </c>
       <c r="E93" t="s" s="7">
-        <v>171</v>
+        <v>49</v>
       </c>
       <c r="F93" t="s" s="7">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="94" ht="18.0" customHeight="true">
@@ -2734,19 +2743,19 @@
         <v>92.0</v>
       </c>
       <c r="B94" t="s" s="9">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C94" t="s" s="9">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D94" t="n" s="10">
-        <v>1601.0</v>
+        <v>1594.0</v>
       </c>
       <c r="E94" t="s" s="9">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F94" t="s" s="9">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="95" ht="18.0" customHeight="true">
@@ -2754,60 +2763,80 @@
         <v>93.0</v>
       </c>
       <c r="B95" t="s" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C95" t="s" s="7">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D95" t="n" s="8">
+        <v>1601.0</v>
+      </c>
+      <c r="E95" t="s" s="7">
+        <v>176</v>
+      </c>
+      <c r="F95" t="s" s="7">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="96" ht="18.0" customHeight="true">
+      <c r="A96" t="n" s="10">
+        <v>94.0</v>
+      </c>
+      <c r="B96" t="s" s="9">
+        <v>177</v>
+      </c>
+      <c r="C96" t="s" s="9">
+        <v>128</v>
+      </c>
+      <c r="D96" t="n" s="10">
         <v>1644.0</v>
       </c>
-      <c r="E95" t="s" s="7">
-        <v>175</v>
-      </c>
-      <c r="F95" t="s" s="7">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="E97" t="s" s="11">
-        <v>176</v>
-      </c>
-      <c r="F97" t="n" s="12">
-        <v>93.0</v>
+      <c r="E96" t="s" s="9">
+        <v>178</v>
+      </c>
+      <c r="F96" t="s" s="9">
+        <v>130</v>
       </c>
     </row>
     <row r="98">
-      <c r="E98" t="s" s="13">
-        <v>177</v>
-      </c>
-      <c r="F98" t="n" s="14">
-        <v>71.0</v>
+      <c r="E98" t="s" s="11">
+        <v>179</v>
+      </c>
+      <c r="F98" t="n" s="12">
+        <v>94.0</v>
       </c>
     </row>
     <row r="99">
-      <c r="E99" t="s" s="15">
-        <v>178</v>
-      </c>
-      <c r="F99" t="n" s="16">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s" s="3">
-        <v>179</v>
+      <c r="E99" t="s" s="13">
+        <v>180</v>
+      </c>
+      <c r="F99" t="n" s="14">
+        <v>67.0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="E100" t="s" s="15">
+        <v>181</v>
+      </c>
+      <c r="F100" t="n" s="16">
+        <v>0.0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="s" s="5">
-        <v>180</v>
+      <c r="A102" t="s" s="3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="5">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A101:F101"/>
     <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A103:F103"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -2815,7 +2844,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="5.859375" customWidth="true"/>
@@ -2827,7 +2856,7 @@
   <sheetData>
     <row r="1" ht="26.0" customHeight="true">
       <c r="A1" t="s" s="1">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" ht="20.0" customHeight="true">
@@ -3099,7 +3128,7 @@
         <v>0.0</v>
       </c>
       <c r="E17" t="s" s="3">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" ht="18.0" customHeight="true">
@@ -3107,16 +3136,16 @@
         <v>16.0</v>
       </c>
       <c r="B18" t="s" s="3">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D18" t="n" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="s" s="3">
         <v>40</v>
-      </c>
-      <c r="C18" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D18" t="n" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="E18" t="s" s="3">
-        <v>39</v>
       </c>
     </row>
     <row r="19" ht="18.0" customHeight="true">
@@ -3133,7 +3162,7 @@
         <v>0.0</v>
       </c>
       <c r="E19" t="s" s="3">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" ht="18.0" customHeight="true">
@@ -3141,7 +3170,7 @@
         <v>18.0</v>
       </c>
       <c r="B20" t="s" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s" s="3">
         <v>14</v>
@@ -3150,7 +3179,7 @@
         <v>0.0</v>
       </c>
       <c r="E20" t="s" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" ht="18.0" customHeight="true">
@@ -3158,7 +3187,7 @@
         <v>19.0</v>
       </c>
       <c r="B21" t="s" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s" s="3">
         <v>14</v>
@@ -3167,7 +3196,7 @@
         <v>0.0</v>
       </c>
       <c r="E21" t="s" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" ht="18.0" customHeight="true">
@@ -3175,7 +3204,7 @@
         <v>20.0</v>
       </c>
       <c r="B22" t="s" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s" s="3">
         <v>14</v>
@@ -3192,7 +3221,7 @@
         <v>21.0</v>
       </c>
       <c r="B23" t="s" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s" s="3">
         <v>14</v>
@@ -3201,7 +3230,7 @@
         <v>0.0</v>
       </c>
       <c r="E23" t="s" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" ht="18.0" customHeight="true">
@@ -3209,7 +3238,7 @@
         <v>22.0</v>
       </c>
       <c r="B24" t="s" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s" s="3">
         <v>14</v>
@@ -3218,7 +3247,7 @@
         <v>0.0</v>
       </c>
       <c r="E24" t="s" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" ht="18.0" customHeight="true">
@@ -3226,7 +3255,7 @@
         <v>23.0</v>
       </c>
       <c r="B25" t="s" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s" s="3">
         <v>14</v>
@@ -3235,7 +3264,7 @@
         <v>0.0</v>
       </c>
       <c r="E25" t="s" s="3">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" ht="18.0" customHeight="true">
@@ -3243,7 +3272,7 @@
         <v>24.0</v>
       </c>
       <c r="B26" t="s" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s" s="3">
         <v>14</v>
@@ -3252,7 +3281,7 @@
         <v>0.0</v>
       </c>
       <c r="E26" t="s" s="3">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" ht="18.0" customHeight="true">
@@ -3260,7 +3289,7 @@
         <v>25.0</v>
       </c>
       <c r="B27" t="s" s="3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s" s="3">
         <v>14</v>
@@ -3269,7 +3298,7 @@
         <v>0.0</v>
       </c>
       <c r="E27" t="s" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" ht="18.0" customHeight="true">
@@ -3277,7 +3306,7 @@
         <v>26.0</v>
       </c>
       <c r="B28" t="s" s="3">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s" s="3">
         <v>14</v>
@@ -3286,7 +3315,7 @@
         <v>0.0</v>
       </c>
       <c r="E28" t="s" s="3">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" ht="18.0" customHeight="true">
@@ -3294,7 +3323,7 @@
         <v>27.0</v>
       </c>
       <c r="B29" t="s" s="3">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s" s="3">
         <v>14</v>
@@ -3311,7 +3340,7 @@
         <v>28.0</v>
       </c>
       <c r="B30" t="s" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s" s="3">
         <v>14</v>
@@ -3320,7 +3349,7 @@
         <v>0.0</v>
       </c>
       <c r="E30" t="s" s="3">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" ht="18.0" customHeight="true">
@@ -3405,7 +3434,7 @@
         <v>0.0</v>
       </c>
       <c r="E35" t="s" s="3">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" ht="18.0" customHeight="true">
@@ -3413,16 +3442,16 @@
         <v>34.0</v>
       </c>
       <c r="B36" t="s" s="3">
+        <v>69</v>
+      </c>
+      <c r="C36" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D36" t="n" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E36" t="s" s="3">
         <v>68</v>
-      </c>
-      <c r="C36" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D36" t="n" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="E36" t="s" s="3">
-        <v>69</v>
       </c>
     </row>
     <row r="37" ht="18.0" customHeight="true">
@@ -3439,7 +3468,7 @@
         <v>0.0</v>
       </c>
       <c r="E37" t="s" s="3">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" ht="18.0" customHeight="true">
@@ -3447,7 +3476,7 @@
         <v>36.0</v>
       </c>
       <c r="B38" t="s" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" t="s" s="3">
         <v>14</v>
@@ -3456,7 +3485,7 @@
         <v>0.0</v>
       </c>
       <c r="E38" t="s" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" ht="18.0" customHeight="true">
@@ -3464,7 +3493,7 @@
         <v>37.0</v>
       </c>
       <c r="B39" t="s" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C39" t="s" s="3">
         <v>14</v>
@@ -3473,7 +3502,7 @@
         <v>0.0</v>
       </c>
       <c r="E39" t="s" s="3">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" ht="18.0" customHeight="true">
@@ -3481,7 +3510,7 @@
         <v>38.0</v>
       </c>
       <c r="B40" t="s" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C40" t="s" s="3">
         <v>14</v>
@@ -3490,7 +3519,7 @@
         <v>0.0</v>
       </c>
       <c r="E40" t="s" s="3">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" ht="18.0" customHeight="true">
@@ -3498,7 +3527,7 @@
         <v>39.0</v>
       </c>
       <c r="B41" t="s" s="3">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C41" t="s" s="3">
         <v>14</v>
@@ -3507,7 +3536,7 @@
         <v>0.0</v>
       </c>
       <c r="E41" t="s" s="3">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" ht="18.0" customHeight="true">
@@ -3515,7 +3544,7 @@
         <v>40.0</v>
       </c>
       <c r="B42" t="s" s="3">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s" s="3">
         <v>14</v>
@@ -3524,7 +3553,7 @@
         <v>0.0</v>
       </c>
       <c r="E42" t="s" s="3">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" ht="18.0" customHeight="true">
@@ -3532,16 +3561,16 @@
         <v>41.0</v>
       </c>
       <c r="B43" t="s" s="3">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C43" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D43" t="n" s="4">
-        <v>0.0</v>
+        <v>61.0</v>
       </c>
       <c r="E43" t="s" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" ht="18.0" customHeight="true">
@@ -3549,16 +3578,16 @@
         <v>42.0</v>
       </c>
       <c r="B44" t="s" s="3">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D44" t="n" s="4">
-        <v>0.0</v>
+        <v>61.0</v>
       </c>
       <c r="E44" t="s" s="3">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" ht="18.0" customHeight="true">
@@ -3566,16 +3595,16 @@
         <v>43.0</v>
       </c>
       <c r="B45" t="s" s="3">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D45" t="n" s="4">
-        <v>0.0</v>
+        <v>124.0</v>
       </c>
       <c r="E45" t="s" s="3">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" ht="18.0" customHeight="true">
@@ -3583,16 +3612,16 @@
         <v>44.0</v>
       </c>
       <c r="B46" t="s" s="3">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D46" t="n" s="4">
-        <v>0.0</v>
+        <v>126.0</v>
       </c>
       <c r="E46" t="s" s="3">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" ht="18.0" customHeight="true">
@@ -3600,16 +3629,16 @@
         <v>45.0</v>
       </c>
       <c r="B47" t="s" s="3">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C47" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D47" t="n" s="4">
-        <v>60.0</v>
+        <v>126.0</v>
       </c>
       <c r="E47" t="s" s="3">
-        <v>88</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" ht="18.0" customHeight="true">
@@ -3617,16 +3646,16 @@
         <v>46.0</v>
       </c>
       <c r="B48" t="s" s="3">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C48" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D48" t="n" s="4">
-        <v>61.0</v>
+        <v>148.0</v>
       </c>
       <c r="E48" t="s" s="3">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" ht="18.0" customHeight="true">
@@ -3634,16 +3663,16 @@
         <v>47.0</v>
       </c>
       <c r="B49" t="s" s="3">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D49" t="n" s="4">
-        <v>61.0</v>
+        <v>154.0</v>
       </c>
       <c r="E49" t="s" s="3">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" ht="18.0" customHeight="true">
@@ -3651,16 +3680,16 @@
         <v>48.0</v>
       </c>
       <c r="B50" t="s" s="3">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C50" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D50" t="n" s="4">
-        <v>126.0</v>
+        <v>159.0</v>
       </c>
       <c r="E50" t="s" s="3">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" ht="18.0" customHeight="true">
@@ -3668,16 +3697,16 @@
         <v>49.0</v>
       </c>
       <c r="B51" t="s" s="3">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C51" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D51" t="n" s="4">
-        <v>154.0</v>
+        <v>184.0</v>
       </c>
       <c r="E51" t="s" s="3">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" ht="18.0" customHeight="true">
@@ -3685,16 +3714,16 @@
         <v>50.0</v>
       </c>
       <c r="B52" t="s" s="3">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D52" t="n" s="4">
-        <v>159.0</v>
+        <v>215.0</v>
       </c>
       <c r="E52" t="s" s="3">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" ht="18.0" customHeight="true">
@@ -3702,16 +3731,16 @@
         <v>51.0</v>
       </c>
       <c r="B53" t="s" s="3">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D53" t="n" s="4">
-        <v>184.0</v>
+        <v>215.0</v>
       </c>
       <c r="E53" t="s" s="3">
-        <v>100</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54" ht="18.0" customHeight="true">
@@ -3719,7 +3748,7 @@
         <v>52.0</v>
       </c>
       <c r="B54" t="s" s="3">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C54" t="s" s="3">
         <v>14</v>
@@ -3728,7 +3757,7 @@
         <v>215.0</v>
       </c>
       <c r="E54" t="s" s="3">
-        <v>102</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55" ht="18.0" customHeight="true">
@@ -3759,10 +3788,10 @@
         <v>14</v>
       </c>
       <c r="D56" t="n" s="4">
-        <v>219.0</v>
+        <v>236.0</v>
       </c>
       <c r="E56" t="s" s="3">
-        <v>106</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" ht="18.0" customHeight="true">
@@ -3770,16 +3799,16 @@
         <v>55.0</v>
       </c>
       <c r="B57" t="s" s="3">
+        <v>106</v>
+      </c>
+      <c r="C57" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D57" t="n" s="4">
+        <v>272.0</v>
+      </c>
+      <c r="E57" t="s" s="3">
         <v>107</v>
-      </c>
-      <c r="C57" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D57" t="n" s="4">
-        <v>236.0</v>
-      </c>
-      <c r="E57" t="s" s="3">
-        <v>54</v>
       </c>
     </row>
     <row r="58" ht="18.0" customHeight="true">
@@ -3793,10 +3822,10 @@
         <v>14</v>
       </c>
       <c r="D58" t="n" s="4">
-        <v>278.0</v>
+        <v>282.0</v>
       </c>
       <c r="E58" t="s" s="3">
-        <v>75</v>
+        <v>109</v>
       </c>
     </row>
     <row r="59" ht="18.0" customHeight="true">
@@ -3804,16 +3833,16 @@
         <v>57.0</v>
       </c>
       <c r="B59" t="s" s="3">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C59" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D59" t="n" s="4">
-        <v>282.0</v>
+        <v>338.0</v>
       </c>
       <c r="E59" t="s" s="3">
-        <v>110</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" ht="18.0" customHeight="true">
@@ -3844,7 +3873,7 @@
         <v>14</v>
       </c>
       <c r="D61" t="n" s="4">
-        <v>375.0</v>
+        <v>431.0</v>
       </c>
       <c r="E61" t="s" s="3">
         <v>114</v>
@@ -3861,10 +3890,10 @@
         <v>14</v>
       </c>
       <c r="D62" t="n" s="4">
-        <v>401.0</v>
+        <v>468.0</v>
       </c>
       <c r="E62" t="s" s="3">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" ht="18.0" customHeight="true">
@@ -3872,16 +3901,16 @@
         <v>61.0</v>
       </c>
       <c r="B63" t="s" s="3">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C63" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D63" t="n" s="4">
-        <v>468.0</v>
+        <v>502.0</v>
       </c>
       <c r="E63" t="s" s="3">
-        <v>117</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" ht="18.0" customHeight="true">
@@ -3895,10 +3924,10 @@
         <v>14</v>
       </c>
       <c r="D64" t="n" s="4">
-        <v>502.0</v>
+        <v>529.0</v>
       </c>
       <c r="E64" t="s" s="3">
-        <v>72</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" ht="18.0" customHeight="true">
@@ -3906,16 +3935,16 @@
         <v>63.0</v>
       </c>
       <c r="B65" t="s" s="3">
+        <v>120</v>
+      </c>
+      <c r="C65" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D65" t="n" s="4">
+        <v>555.0</v>
+      </c>
+      <c r="E65" t="s" s="3">
         <v>119</v>
-      </c>
-      <c r="C65" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D65" t="n" s="4">
-        <v>589.0</v>
-      </c>
-      <c r="E65" t="s" s="3">
-        <v>120</v>
       </c>
     </row>
     <row r="66" ht="18.0" customHeight="true">
@@ -3926,13 +3955,13 @@
         <v>121</v>
       </c>
       <c r="C66" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D66" t="n" s="4">
+        <v>589.0</v>
+      </c>
+      <c r="E66" t="s" s="3">
         <v>122</v>
-      </c>
-      <c r="D66" t="n" s="4">
-        <v>726.0</v>
-      </c>
-      <c r="E66" t="s" s="3">
-        <v>123</v>
       </c>
     </row>
     <row r="67" ht="18.0" customHeight="true">
@@ -3940,16 +3969,16 @@
         <v>65.0</v>
       </c>
       <c r="B67" t="s" s="3">
+        <v>123</v>
+      </c>
+      <c r="C67" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D67" t="n" s="4">
+        <v>808.0</v>
+      </c>
+      <c r="E67" t="s" s="3">
         <v>124</v>
-      </c>
-      <c r="C67" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D67" t="n" s="4">
-        <v>777.0</v>
-      </c>
-      <c r="E67" t="s" s="3">
-        <v>82</v>
       </c>
     </row>
     <row r="68" ht="18.0" customHeight="true">
@@ -3963,10 +3992,10 @@
         <v>14</v>
       </c>
       <c r="D68" t="n" s="4">
-        <v>808.0</v>
+        <v>865.0</v>
       </c>
       <c r="E68" t="s" s="3">
-        <v>126</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" ht="18.0" customHeight="true">
@@ -3974,84 +4003,16 @@
         <v>67.0</v>
       </c>
       <c r="B69" t="s" s="3">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C69" t="s" s="3">
         <v>14</v>
       </c>
       <c r="D69" t="n" s="4">
-        <v>835.0</v>
+        <v>899.0</v>
       </c>
       <c r="E69" t="s" s="3">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="70" ht="18.0" customHeight="true">
-      <c r="A70" t="n" s="4">
-        <v>68.0</v>
-      </c>
-      <c r="B70" t="s" s="3">
-        <v>128</v>
-      </c>
-      <c r="C70" t="s" s="3">
-        <v>129</v>
-      </c>
-      <c r="D70" t="n" s="4">
-        <v>957.0</v>
-      </c>
-      <c r="E70" t="s" s="3">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="71" ht="18.0" customHeight="true">
-      <c r="A71" t="n" s="4">
-        <v>69.0</v>
-      </c>
-      <c r="B71" t="s" s="3">
-        <v>131</v>
-      </c>
-      <c r="C71" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D71" t="n" s="4">
-        <v>1061.0</v>
-      </c>
-      <c r="E71" t="s" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="72" ht="18.0" customHeight="true">
-      <c r="A72" t="n" s="4">
-        <v>70.0</v>
-      </c>
-      <c r="B72" t="s" s="3">
-        <v>132</v>
-      </c>
-      <c r="C72" t="s" s="3">
-        <v>8</v>
-      </c>
-      <c r="D72" t="n" s="4">
-        <v>1133.0</v>
-      </c>
-      <c r="E72" t="s" s="3">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="73" ht="18.0" customHeight="true">
-      <c r="A73" t="n" s="4">
-        <v>71.0</v>
-      </c>
-      <c r="B73" t="s" s="3">
-        <v>134</v>
-      </c>
-      <c r="C73" t="s" s="3">
-        <v>122</v>
-      </c>
-      <c r="D73" t="n" s="4">
-        <v>1148.0</v>
-      </c>
-      <c r="E73" t="s" s="3">
-        <v>135</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -4076,7 +4037,7 @@
   <sheetData>
     <row r="1" ht="26.0" customHeight="true">
       <c r="A1" t="s" s="1">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" ht="20.0" customHeight="true">
